--- a/data/trans_camb/IP16A09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 0,0</t>
+          <t>-20,73; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 0,0</t>
+          <t>-24,23; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 0,0</t>
+          <t>-18,88; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 0,0</t>
+          <t>-20,37; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,73; -1,84</t>
+          <t>-15,92; -1,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,72; -1,78</t>
+          <t>-14,91; -1,73</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 6,2</t>
+          <t>-9,65; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 11,94</t>
+          <t>-6,48; 12,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 0,0</t>
+          <t>-22,76; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 12,56</t>
+          <t>-8,39; 12,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 4,25</t>
+          <t>-6,74; 4,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 9,95</t>
+          <t>-4,42; 10,57</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 3,99</t>
+          <t>-28,37; 4,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 0,0</t>
+          <t>-33,75; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 11,7</t>
+          <t>-5,87; 14,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 23,62</t>
+          <t>-5,79; 24,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 6,06</t>
+          <t>-10,25; 5,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 6,06</t>
+          <t>-9,69; 6,68</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 6,35</t>
+          <t>-4,57; 6,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 3,64</t>
+          <t>-7,21; 2,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 4,42</t>
+          <t>-4,56; 4,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 3,29</t>
+          <t>-6,72; 3,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,32</t>
+          <t>-3,12; 4,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,71</t>
+          <t>-3,81; 2,96</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,41; -2,68</t>
+          <t>-21,93; -2,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,41; -2,68</t>
+          <t>-21,93; -2,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,08</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 0,61</t>
+          <t>-9,95; 0,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,62; -1,2</t>
+          <t>-11,82; -1,2</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,49; 38,63</t>
+          <t>4,57; 38,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,49; 23,29</t>
+          <t>2,45; 23,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,35</t>
+          <t>-6,47; 0,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,25; -0,43</t>
+          <t>-6,87; -0,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,84</t>
+          <t>-2,26; 3,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,54</t>
+          <t>-3,35; 2,53</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,11</t>
+          <t>-3,46; 1,22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,3</t>
+          <t>-3,94; 0,37</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-90,21; 52,06</t>
+          <t>-89,85; 43,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-93,52; 10,54</t>
+          <t>-91,75; 40,16</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-66,08; 452,05</t>
+          <t>-64,01; 407,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-83,82; 323,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-67,36; 58,4</t>
+          <t>-68,13; 64,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-81,39; 25,16</t>
+          <t>-81,99; 29,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 0,0</t>
+          <t>-20,62; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 0,0</t>
+          <t>-20,24; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 0,0</t>
+          <t>-18,73; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 0,0</t>
+          <t>-21,36; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -1,72</t>
+          <t>-14,77; -1,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,91; -1,73</t>
+          <t>-15,9; -1,77</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 6,17</t>
+          <t>-9,7; 6,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 12,11</t>
+          <t>-6,56; 11,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 0,0</t>
+          <t>-21,59; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 12,71</t>
+          <t>-8,16; 12,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 4,26</t>
+          <t>-6,95; 4,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 10,57</t>
+          <t>-4,85; 9,37</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 4,12</t>
+          <t>-27,76; 4,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 0,0</t>
+          <t>-32,41; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 14,82</t>
+          <t>-5,86; 14,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 24,03</t>
+          <t>-5,87; 26,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 5,69</t>
+          <t>-10,16; 5,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 6,68</t>
+          <t>-10,76; 5,93</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 6,29</t>
+          <t>-4,69; 6,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 2,99</t>
+          <t>-7,32; 3,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 4,52</t>
+          <t>-4,89; 4,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 3,27</t>
+          <t>-5,15; 3,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 4,2</t>
+          <t>-3,1; 4,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,96</t>
+          <t>-3,9; 3,05</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,61; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,93; -2,63</t>
+          <t>-23,84; -2,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,93; -2,63</t>
+          <t>-23,84; -2,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 0,63</t>
+          <t>-9,98; 0,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -1,2</t>
+          <t>-10,33; -1,2</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,57; 38,42</t>
+          <t>4,42; 37,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,45; 23,0</t>
+          <t>2,78; 25,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 0,53</t>
+          <t>-7,18; 0,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,87; -0,33</t>
+          <t>-7,08; -0,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,64</t>
+          <t>-2,66; 3,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,53</t>
+          <t>-3,32; 2,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,22</t>
+          <t>-3,48; 1,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,37</t>
+          <t>-4,06; 0,19</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-89,85; 43,09</t>
+          <t>-91,44; 42,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-91,75; 40,16</t>
+          <t>-93,53; -2,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 407,38</t>
+          <t>-71,43; 341,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,57; 287,75</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-68,13; 64,63</t>
+          <t>-67,6; 52,1</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-81,99; 29,98</t>
+          <t>-80,51; 21,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Clase-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumieron medicamentos para los vómitos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-6,21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-6,36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-6,36</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,21</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 0,0</t>
+          <t>-18,8; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 0,0</t>
+          <t>-19,23; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 0,0</t>
+          <t>-20,57; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 0,0</t>
+          <t>-21,94; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,77; -1,73</t>
+          <t>-15,73; -1,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,9; -1,77</t>
+          <t>-14,72; -1,78</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,62</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,66</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,08</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2,57</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,62</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 6,21</t>
+          <t>-20,52; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 11,83</t>
+          <t>-8,2; 12,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 0,0</t>
+          <t>-9,64; 6,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 12,86</t>
+          <t>-6,71; 11,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 4,24</t>
+          <t>-6,93; 4,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 9,37</t>
+          <t>-4,48; 9,95</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>73,42%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-2,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>81,64%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,02</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-6,74</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-10,67</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,02</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 4,64</t>
+          <t>-5,96; 11,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,41; 0,0</t>
+          <t>-5,85; 23,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 14,62</t>
+          <t>-27,87; 3,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 26,03</t>
+          <t>-33,55; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 5,88</t>
+          <t>-9,16; 6,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 5,93</t>
+          <t>-10,09; 6,06</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>103,1%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-63,17%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>103,1%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,12</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 6,31</t>
+          <t>-4,42; 4,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,1</t>
+          <t>-5,26; 3,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 4,59</t>
+          <t>-4,69; 6,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,36</t>
+          <t>-6,35; 3,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 4,34</t>
+          <t>-2,82; 4,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 3,05</t>
+          <t>-3,99; 2,71</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>32,88%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-2,9%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>64,04%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-5,58%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>32,88%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-2,9%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-90,61; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,92</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-8,7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-8,7</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-23,84; -2,68</t>
+          <t>0,0; 9,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23,84; -2,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,78</t>
+          <t>-21,41; -2,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,41; -2,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,42</t>
+          <t>-9,29; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,33; -1,2</t>
+          <t>-10,62; -1,2</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>18,26</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>18,26</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,49; 38,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,42; 37,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,78; 25,07</t>
+          <t>2,49; 23,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-2,77</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-3,28</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 0,39</t>
+          <t>-2,31; 3,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -0,33</t>
+          <t>-2,92; 2,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 3,45</t>
+          <t>-6,92; 0,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 2,06</t>
+          <t>-7,25; -0,43</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,1</t>
+          <t>-3,31; 1,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,19</t>
+          <t>-4,1; 0,3</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>28,99%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-17,57%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-58,53%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-69,26%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>28,99%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-17,57%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-91,44; 42,3</t>
+          <t>-66,08; 452,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-93,53; -2,98</t>
+          <t>-83,82; 323,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 341,44</t>
+          <t>-90,21; 52,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-88,57; 287,75</t>
+          <t>-93,52; 10,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-67,6; 52,1</t>
+          <t>-67,36; 58,4</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-80,51; 21,12</t>
+          <t>-81,39; 25,16</t>
         </is>
       </c>
     </row>
